--- a/hasil_jadwal.xlsx
+++ b/hasil_jadwal.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Jadwal Bulan August" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Jadwal Bulan September" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF34"/>
+  <dimension ref="A1:AE34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,9 +519,6 @@
       <c r="AE1" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="n">
-        <v>31</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -531,157 +528,152 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
     </row>
@@ -693,47 +685,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -743,107 +735,102 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>SOC6</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>P7</t>
         </is>
       </c>
     </row>
@@ -855,7 +842,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -870,12 +857,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -885,22 +872,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -910,69 +897,69 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>P8</t>
@@ -980,17 +967,17 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1000,12 +987,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
     </row>
@@ -1017,17 +999,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1047,47 +1029,47 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1102,47 +1084,47 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1157,17 +1139,12 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -1179,157 +1156,152 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1313,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1351,22 +1323,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1376,77 +1348,77 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>Cuti</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1456,12 +1428,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1471,27 +1443,22 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
     </row>
@@ -1503,102 +1470,102 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1608,12 +1575,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1623,12 +1590,12 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1638,22 +1605,17 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
           <t>P8</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>P6</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1627,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1685,107 +1647,107 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1810,12 +1772,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>SOC6</t>
+          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1784,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1842,19 +1799,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>P7</t>
@@ -1862,7 +1819,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1872,12 +1829,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1887,22 +1844,22 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1912,27 +1869,27 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1942,42 +1899,37 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>P6</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -1994,112 +1946,112 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -2109,17 +2061,17 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2129,17 +2081,12 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
     </row>
@@ -2156,17 +2103,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2176,7 +2123,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2186,27 +2133,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2216,22 +2163,22 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2241,67 +2188,62 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2265,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2333,137 +2275,132 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>P11</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -2475,157 +2412,152 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
     </row>
@@ -2637,157 +2569,152 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
     </row>
@@ -2799,157 +2726,152 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
         <is>
           <t>SOCM</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -2961,22 +2883,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2986,132 +2908,127 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
         <is>
           <t>SOC2</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>S12</t>
         </is>
       </c>
     </row>
@@ -3123,155 +3040,150 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
       <c r="AE18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
         <is>
           <t>Libur</t>
         </is>
@@ -3285,157 +3197,152 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3354,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3457,17 +3364,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3477,7 +3384,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3487,59 +3394,59 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -3552,32 +3459,32 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3587,17 +3494,12 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
     </row>
@@ -3609,157 +3511,152 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3668,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3781,17 +3678,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3801,87 +3698,87 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3891,7 +3788,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3901,27 +3798,22 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
     </row>
@@ -3933,117 +3825,117 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
         <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -4053,12 +3945,12 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -4073,17 +3965,12 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -4095,157 +3982,152 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>SOCM</t>
+          <t>P10</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4139,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4267,122 +4149,122 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -4392,22 +4274,17 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
           <t>S12</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -4419,122 +4296,122 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -4544,7 +4421,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -4554,7 +4431,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -4563,11 +4440,6 @@
         </is>
       </c>
       <c r="AE26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
@@ -4581,47 +4453,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4631,89 +4503,89 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -4721,15 +4593,10 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
         <is>
           <t>Libur</t>
         </is>
@@ -4743,52 +4610,52 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -4798,7 +4665,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4808,90 +4675,85 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -4905,12 +4767,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4920,27 +4782,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4950,22 +4812,22 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -4975,57 +4837,57 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -5035,27 +4897,22 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -5067,12 +4924,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5082,7 +4939,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5092,22 +4949,22 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -5117,27 +4974,27 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -5147,77 +5004,72 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>SOC2</t>
+          <t>P10</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5081,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5239,52 +5091,52 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -5299,17 +5151,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -5329,55 +5181,50 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
         <is>
           <t>Libur</t>
         </is>
@@ -5391,114 +5238,114 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cuti</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
       <c r="X32" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -5506,12 +5353,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5521,12 +5368,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -5536,12 +5383,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>Libur</t>
+          <t>P11</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5395,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5563,12 +5405,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5578,32 +5420,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -5613,17 +5455,17 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -5633,57 +5475,57 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5693,17 +5535,12 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
     </row>
@@ -5715,42 +5552,42 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5760,42 +5597,42 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -5805,67 +5642,62 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
     </row>

--- a/hasil_jadwal.xlsx
+++ b/hasil_jadwal.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -598,17 +598,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -653,27 +653,27 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -685,22 +685,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -720,67 +720,67 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -825,12 +825,12 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -867,127 +867,127 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -999,22 +999,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1049,32 +1049,32 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>M</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1089,47 +1089,47 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
     </row>
@@ -1156,67 +1156,67 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1226,32 +1226,32 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1261,32 +1261,32 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -1313,152 +1313,152 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Cuti</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>SOC6</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>M</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1540,22 +1540,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1580,17 +1580,17 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1600,22 +1600,22 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
     </row>
@@ -1627,32 +1627,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1662,22 +1662,22 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1727,22 +1727,22 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -1784,52 +1784,52 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1859,27 +1859,27 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1899,37 +1899,37 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P6</t>
         </is>
       </c>
     </row>
@@ -1941,27 +1941,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1981,27 +1981,27 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -2026,52 +2026,52 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
     </row>
@@ -2098,104 +2098,104 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -2255,57 +2255,57 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2320,74 +2320,74 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -2395,12 +2395,12 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
     </row>
@@ -2417,37 +2417,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2457,22 +2457,22 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2487,59 +2487,59 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
       <c r="AB14" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -2569,147 +2569,147 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
           <t>SOC2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>P10</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -2726,22 +2726,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2751,97 +2751,97 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2851,27 +2851,27 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>P7</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2918,117 +2918,117 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>S12</t>
         </is>
       </c>
     </row>
@@ -3040,152 +3040,152 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
     </row>
@@ -3197,152 +3197,152 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -3354,29 +3354,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -3389,102 +3389,102 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P10</t>
         </is>
       </c>
     </row>
@@ -3511,27 +3511,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3546,84 +3546,84 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
         <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
       <c r="Y21" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3646,17 +3646,17 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
     </row>
@@ -3668,42 +3668,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3713,107 +3713,107 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
           <t>SOC2</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>P9</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>M</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3860,97 +3860,97 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
         <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Cuti</t>
         </is>
       </c>
     </row>
@@ -3987,147 +3987,147 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
         <is>
           <t>P11</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>P10</t>
         </is>
       </c>
     </row>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4149,27 +4149,27 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4184,87 +4184,87 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -4274,17 +4274,17 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -4296,144 +4296,144 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="AD26" t="inlineStr">
         <is>
           <t>S12</t>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P7</t>
         </is>
       </c>
     </row>
@@ -4453,24 +4453,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -4478,72 +4478,72 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -4573,17 +4573,17 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -4610,117 +4610,117 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
         <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4730,32 +4730,32 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -4767,152 +4767,152 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
         <is>
           <t>SOCM</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>P8</t>
         </is>
       </c>
     </row>
@@ -4924,47 +4924,47 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4989,52 +4989,52 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -5044,32 +5044,32 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -5081,82 +5081,82 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -5196,37 +5196,37 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
     </row>
@@ -5248,12 +5248,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5273,27 +5273,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5303,22 +5303,22 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -5338,22 +5338,22 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -5405,12 +5405,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5460,17 +5460,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -5505,27 +5505,27 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Cuti</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5587,17 +5587,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5622,27 +5622,27 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">

--- a/hasil_jadwal.xlsx
+++ b/hasil_jadwal.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -558,37 +558,37 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -598,17 +598,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,17 +618,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -643,37 +643,37 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -685,12 +685,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -700,57 +700,57 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -825,12 +825,12 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P9</t>
         </is>
       </c>
     </row>
@@ -842,32 +842,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -877,49 +877,49 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>P8</t>
@@ -927,12 +927,12 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -942,39 +942,39 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>P7</t>
@@ -982,12 +982,12 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -999,22 +999,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1054,57 +1054,57 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1156,82 +1156,82 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1261,32 +1261,32 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -1313,77 +1313,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1495,42 +1495,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1555,67 +1555,67 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -1627,32 +1627,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1667,17 +1667,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1722,57 +1722,57 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
           <t>SOC6</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -1784,22 +1784,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1809,47 +1809,47 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1869,27 +1869,27 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -1946,62 +1946,62 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2011,62 +2011,62 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2113,19 +2113,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2218,32 +2218,32 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
     </row>
@@ -2255,152 +2255,152 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -2412,52 +2412,52 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2497,67 +2497,67 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P9</t>
         </is>
       </c>
     </row>
@@ -2569,67 +2569,67 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2639,17 +2639,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2664,57 +2664,57 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P7</t>
         </is>
       </c>
     </row>
@@ -2726,147 +2726,147 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -2883,12 +2883,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2898,17 +2898,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2918,99 +2918,99 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
         <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="AB17" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -3018,12 +3018,12 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
@@ -3040,127 +3040,127 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
@@ -3197,17 +3197,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3217,132 +3217,132 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
           <t>P11</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>S12</t>
         </is>
       </c>
     </row>
@@ -3354,82 +3354,82 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -3439,27 +3439,27 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -3474,17 +3474,17 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P10</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3556,107 +3556,107 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="Z21" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
     </row>
@@ -3668,62 +3668,62 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3733,17 +3733,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3768,37 +3768,37 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>M</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
     </row>
@@ -3825,134 +3825,134 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
       <c r="AB23" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -3960,17 +3960,17 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>S12</t>
         </is>
       </c>
     </row>
@@ -3982,152 +3982,152 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
     </row>
@@ -4139,52 +4139,52 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -4204,67 +4204,67 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -4274,17 +4274,17 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
     </row>
@@ -4296,109 +4296,109 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="W26" t="inlineStr">
         <is>
           <t>P10</t>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P6</t>
         </is>
       </c>
     </row>
@@ -4453,152 +4453,152 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -4610,152 +4610,152 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
     </row>
@@ -4767,137 +4767,137 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>M</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4924,22 +4924,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4949,97 +4949,97 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -5049,27 +5049,27 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5091,142 +5091,142 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
     </row>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5273,107 +5273,107 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P7</t>
         </is>
       </c>
     </row>
@@ -5395,17 +5395,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5465,37 +5465,37 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -5510,37 +5510,37 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -5552,12 +5552,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5597,17 +5597,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5627,22 +5627,22 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P10</t>
         </is>
       </c>
     </row>

--- a/hasil_jadwal.xlsx
+++ b/hasil_jadwal.xlsx
@@ -528,152 +528,152 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
     </row>
@@ -695,59 +695,59 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -760,77 +760,77 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
     </row>
@@ -842,22 +842,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -872,27 +872,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -917,27 +917,27 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>M</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>M</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -947,47 +947,47 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>SOC6</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>P8</t>
         </is>
       </c>
     </row>
@@ -999,87 +999,87 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1191,39 +1191,39 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>P9</t>
@@ -1236,22 +1236,22 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1261,32 +1261,32 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
     </row>
@@ -1313,22 +1313,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1368,37 +1368,37 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1423,34 +1423,34 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>Cuti</t>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>P9</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1500,32 +1500,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1535,72 +1535,72 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
     </row>
@@ -1627,22 +1627,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1692,34 +1692,34 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -1742,27 +1742,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1784,27 +1784,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1824,17 +1824,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1859,17 +1859,17 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1889,17 +1889,17 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -1946,92 +1946,92 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>SOC6</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2118,32 +2118,32 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -2183,17 +2183,17 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2255,39 +2255,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -2295,97 +2295,97 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>S12</t>
         </is>
       </c>
     </row>
@@ -2412,12 +2412,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2442,104 +2442,104 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
       <c r="AB14" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -2574,97 +2574,97 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -2731,147 +2731,147 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
         <is>
           <t>SOC2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>P7</t>
         </is>
       </c>
     </row>
@@ -2883,12 +2883,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2923,77 +2923,77 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -3003,27 +3003,27 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3065,37 +3065,37 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3105,17 +3105,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -3135,57 +3135,57 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
           <t>P11</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>P10</t>
         </is>
       </c>
     </row>
@@ -3207,142 +3207,142 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
           <t>SOCM</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>M</t>
         </is>
       </c>
     </row>
@@ -3354,152 +3354,152 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
         <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3526,107 +3526,107 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P10</t>
         </is>
       </c>
     </row>
@@ -3673,114 +3673,114 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
         <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
       <c r="Y22" t="inlineStr">
         <is>
           <t>Libur</t>
@@ -3788,12 +3788,12 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>P10</t>
         </is>
       </c>
     </row>
@@ -3825,137 +3825,137 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
         <is>
           <t>P11</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>Libur</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3997,17 +3997,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4017,117 +4017,117 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P8</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4154,42 +4154,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -4204,87 +4204,87 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P9</t>
         </is>
       </c>
     </row>
@@ -4296,102 +4296,102 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>SOC6</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -4406,42 +4406,42 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -4468,17 +4468,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>SOCM</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4498,22 +4498,22 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4528,62 +4528,62 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>SOC2</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P9</t>
         </is>
       </c>
     </row>
@@ -4625,82 +4625,82 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4710,27 +4710,27 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>SOC2</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4745,17 +4745,17 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
     </row>
@@ -4772,147 +4772,147 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>SOCM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>SOC6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>SOC2</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>SOCM</t>
+          <t>S12</t>
         </is>
       </c>
     </row>
@@ -4924,152 +4924,152 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>SOC2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>SOC6</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>SOCM</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
         <is>
           <t>SOC2</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>SOCM</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>SOC6</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P10</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5126,17 +5126,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -5166,17 +5166,17 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -5186,12 +5186,12 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -5211,22 +5211,22 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>Libur</t>
         </is>
       </c>
     </row>
@@ -5238,94 +5238,94 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Cuti</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Libur</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Cuti</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Libur</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
       <c r="T32" t="inlineStr">
         <is>
           <t>M</t>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -5395,27 +5395,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -5450,17 +5450,17 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -5475,17 +5475,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5562,27 +5562,27 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Libur</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -5622,17 +5622,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Libur</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
